--- a/analysis/aggregate/sp-PRF.xlsx
+++ b/analysis/aggregate/sp-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8867783480326763</v>
+        <v>0.8731855776926384</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02592792753159446</v>
+        <v>0.01058400034708012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8811764705882353</v>
+        <v>0.8658823529411765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01341382853057808</v>
+        <v>0.002630668208823276</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8838861445383579</v>
+        <v>0.8694862649260674</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01829360190281198</v>
+        <v>0.004864591343310202</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -571,22 +571,22 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8867783480326763</v>
+        <v>0.8321567817990001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02592792753159446</v>
+        <v>0.006694621366193838</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8811764705882353</v>
+        <v>0.8341176470588236</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01341382853057808</v>
+        <v>0.009665692191267675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8838861445383579</v>
+        <v>0.8331257342570954</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01829360190281198</v>
+        <v>0.007636504171103083</v>
       </c>
     </row>
     <row r="4">
@@ -597,7 +597,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8737090933934549</v>
+        <v>0.8733973115873568</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01985956362372797</v>
+        <v>0.008503556883181067</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8694117647058823</v>
+        <v>0.868235294117647</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01684449536856039</v>
+        <v>0.006706914265289072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8714851224024066</v>
+        <v>0.8708025385364913</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01610553403873241</v>
+        <v>0.007198359601894137</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -677,22 +677,22 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8737090933934549</v>
+        <v>0.8249818540933411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01985956362372797</v>
+        <v>0.007666935781775983</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8694117647058823</v>
+        <v>0.831764705882353</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01684449536856039</v>
+        <v>0.01068582477916763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8714851224024066</v>
+        <v>0.8283409199676809</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01610553403873241</v>
+        <v>0.00820623919896921</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -727,25 +727,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9000371949656881</v>
+        <v>0.8907717197225338</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01915704588943443</v>
+        <v>0.01127565102024195</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8662857142857142</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01234426799696728</v>
+        <v>0.01434274331201271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8927706289369955</v>
+        <v>0.8783113374980991</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01410546869176214</v>
+        <v>0.01086186172149496</v>
       </c>
     </row>
     <row r="7">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -783,22 +783,22 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8961661196089141</v>
+        <v>0.8907717197225338</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0187128412459609</v>
+        <v>0.01127565102024195</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8857142857142858</v>
+        <v>0.8662857142857142</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01069044967649694</v>
+        <v>0.01434274331201271</v>
       </c>
       <c r="L7" t="n">
-        <v>0.890854679787773</v>
+        <v>0.8783113374980991</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01294517249683232</v>
+        <v>0.01086186172149496</v>
       </c>
     </row>
     <row r="8">
@@ -809,7 +809,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9040974529346621</v>
+        <v>0.8560459099085259</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02114599019157313</v>
+        <v>0.02354858102072504</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.8662857142857142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.005714285714285658</v>
+        <v>0.01184939505904442</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8918091425413663</v>
+        <v>0.8609768579788248</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01215976830066947</v>
+        <v>0.01348744680232128</v>
       </c>
     </row>
     <row r="9">
@@ -862,48 +862,472 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8560459099085259</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02354858102072504</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8662857142857142</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01184939505904442</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8609768579788248</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01348744680232128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8867783480326763</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02592792753159446</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8811764705882353</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01341382853057808</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8838861445383579</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01829360190281198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8867783480326763</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.02592792753159446</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8811764705882353</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01341382853057808</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8838861445383579</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01829360190281198</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8737090933934549</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01985956362372797</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8694117647058823</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.01684449536856039</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8714851224024066</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01610553403873241</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8737090933934549</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01985956362372797</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8694117647058823</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01684449536856039</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8714851224024066</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01610553403873241</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9000371949656881</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01915704588943443</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01234426799696728</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8927706289369955</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01410546869176214</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8961661196089141</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0187128412459609</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8857142857142858</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01069044967649694</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.890854679787773</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.01294517249683232</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.9040974529346621</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.02114599019157313</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.8800000000000001</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.005714285714285658</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.8918091425413663</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
+        <v>0.01215976830066947</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9040974529346621</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.02114599019157313</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.005714285714285658</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8918091425413663</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.01215976830066947</v>
       </c>
     </row>

--- a/analysis/aggregate/sp-PRF.xlsx
+++ b/analysis/aggregate/sp-PRF.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,22 +518,22 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8731855776926384</v>
+        <v>0.8731974074405733</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01058400034708012</v>
+        <v>0.02065888893166557</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8658823529411765</v>
+        <v>0.8647058823529411</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002630668208823276</v>
+        <v>0.01499711621644939</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8694862649260674</v>
+        <v>0.8688356294898911</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004864591343310202</v>
+        <v>0.01476499533794843</v>
       </c>
     </row>
     <row r="3">
@@ -554,39 +554,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8321567817990001</v>
+        <v>0.8747203944656079</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006694621366193838</v>
+        <v>0.0203224888085293</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8341176470588236</v>
+        <v>0.868235294117647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009665692191267675</v>
+        <v>0.008921029934178306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8331257342570954</v>
+        <v>0.8713851733795137</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007636504171103083</v>
+        <v>0.01250164965122858</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +612,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -624,22 +624,22 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8733973115873568</v>
+        <v>0.8791192945592762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008503556883181067</v>
+        <v>0.01487780696917466</v>
       </c>
       <c r="J4" t="n">
-        <v>0.868235294117647</v>
+        <v>0.8705882352941176</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006706914265289072</v>
+        <v>0.007204381596421137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8708025385364913</v>
+        <v>0.8747423706983127</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007198359601894137</v>
+        <v>0.006072130204107356</v>
       </c>
     </row>
     <row r="5">
@@ -670,29 +670,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8249818540933411</v>
+        <v>0.8645742099555559</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007666935781775983</v>
+        <v>0.01207888556398817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.831764705882353</v>
+        <v>0.8635294117647059</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01068582477916763</v>
+        <v>0.0134138285305781</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8283409199676809</v>
+        <v>0.8640294383150218</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00820623919896921</v>
+        <v>0.0117805250397328</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +730,22 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8907717197225338</v>
+        <v>0.8930154480873498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01127565102024195</v>
+        <v>0.01530422007419065</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8662857142857142</v>
+        <v>0.8754285714285714</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01434274331201271</v>
+        <v>0.007450517034517309</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8783113374980991</v>
+        <v>0.8840533646842171</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01086186172149496</v>
+        <v>0.007195390535008483</v>
       </c>
     </row>
     <row r="7">
@@ -771,34 +771,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8907717197225338</v>
+        <v>0.8953930257315339</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01127565102024195</v>
+        <v>0.005447757325491993</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8662857142857142</v>
+        <v>0.8708571428571428</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01434274331201271</v>
+        <v>0.0111391935369245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8783113374980991</v>
+        <v>0.8829442881317296</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01086186172149496</v>
+        <v>0.008204078337778456</v>
       </c>
     </row>
     <row r="8">
@@ -819,12 +819,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -836,22 +836,22 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8560459099085259</v>
+        <v>0.8935294867764922</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02354858102072504</v>
+        <v>0.005702521186294251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8662857142857142</v>
+        <v>0.8731428571428571</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01184939505904442</v>
+        <v>0.01422845668341572</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8609768579788248</v>
+        <v>0.8831973792864103</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01348744680232128</v>
+        <v>0.009876470609124612</v>
       </c>
     </row>
     <row r="9">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -882,29 +882,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8560459099085259</v>
+        <v>0.8815061522667778</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02354858102072504</v>
+        <v>0.01967145360129622</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8662857142857142</v>
+        <v>0.8651428571428571</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01184939505904442</v>
+        <v>0.01315527363796723</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8609768579788248</v>
+        <v>0.8731684704946007</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01348744680232128</v>
+        <v>0.01371372797948159</v>
       </c>
     </row>
     <row r="10">
@@ -925,7 +925,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -942,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8867783480326763</v>
+        <v>0.8908909889044334</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02592792753159446</v>
+        <v>0.03289849238158567</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8811764705882353</v>
+        <v>0.8823529411764707</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01341382853057808</v>
+        <v>0.02200974933396435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8838861445383579</v>
+        <v>0.8861149667287579</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01829360190281198</v>
+        <v>0.01515117461747082</v>
       </c>
     </row>
     <row r="11">
@@ -978,39 +978,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8867783480326763</v>
+        <v>0.8789496168983442</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02592792753159446</v>
+        <v>0.01649604979027871</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8811764705882353</v>
+        <v>0.8858823529411766</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01341382853057808</v>
+        <v>0.01533929977694741</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8838861445383579</v>
+        <v>0.8822575379890705</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01829360190281198</v>
+        <v>0.00969314459687466</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1048,22 +1048,22 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8737090933934549</v>
+        <v>0.8872473900721782</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01985956362372797</v>
+        <v>0.01440820615560866</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8694117647058823</v>
+        <v>0.8788235294117648</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01684449536856039</v>
+        <v>0.01146681687624583</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8714851224024066</v>
+        <v>0.8829948160036578</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01610553403873241</v>
+        <v>0.01210612575984625</v>
       </c>
     </row>
     <row r="13">
@@ -1094,29 +1094,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8737090933934549</v>
+        <v>0.8645179395512397</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01985956362372797</v>
+        <v>0.02444732254586639</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8694117647058823</v>
+        <v>0.8694117647058824</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01684449536856039</v>
+        <v>0.01684449536856042</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8714851224024066</v>
+        <v>0.8669377140319343</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01610553403873241</v>
+        <v>0.0205251873990517</v>
       </c>
     </row>
     <row r="14">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1151,25 +1151,25 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9000371949656881</v>
+        <v>0.883065996663974</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01915704588943443</v>
+        <v>0.01526158414311968</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8720000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01234426799696728</v>
+        <v>0.01833920746957855</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8927706289369955</v>
+        <v>0.8774910290685023</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01410546869176214</v>
+        <v>0.01666962174910225</v>
       </c>
     </row>
     <row r="15">
@@ -1190,39 +1190,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8961661196089141</v>
+        <v>0.8872390978094191</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0187128412459609</v>
+        <v>0.01032060156918886</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8857142857142858</v>
+        <v>0.8811428571428571</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01069044967649694</v>
+        <v>0.01099164803524074</v>
       </c>
       <c r="L15" t="n">
-        <v>0.890854679787773</v>
+        <v>0.8841704393986598</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01294517249683232</v>
+        <v>0.01012314080693502</v>
       </c>
     </row>
     <row r="16">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1260,22 +1260,22 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9040974529346621</v>
+        <v>0.9001184456387323</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02114599019157313</v>
+        <v>0.02089861420112248</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.8708571428571428</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005714285714285658</v>
+        <v>0.008666143364630331</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8918091425413663</v>
+        <v>0.8850907750665644</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01215976830066947</v>
+        <v>0.008557867116036826</v>
       </c>
     </row>
     <row r="17">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9040974529346621</v>
+        <v>0.9072059066140454</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02114599019157313</v>
+        <v>0.02044624060059865</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.8788571428571428</v>
       </c>
       <c r="K17" t="n">
-        <v>0.005714285714285658</v>
+        <v>0.004780914437337544</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8918091425413663</v>
+        <v>0.8927096923291045</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01215976830066947</v>
+        <v>0.01003594171340425</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/aggregate/sp-PRF.xlsx
+++ b/analysis/aggregate/sp-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,32 +454,92 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision_mean</t>
+          <t>micro_precision_mean</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>precision_std</t>
+          <t>micro_precision_std</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>recall_mean</t>
+          <t>micro_recall_mean</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>recall_std</t>
+          <t>micro_recall_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>f1_mean</t>
+          <t>micro_f1_mean</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>f1_std</t>
+          <t>micro_f1_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_precision_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_precision_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_recall_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>macro_recall_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>macro_f1_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>macro_f1_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>weighted_precision_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>weighted_precision_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>weighted_recall_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>weighted_recall_std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>weighted_f1_mean</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>weighted_f1_std</t>
         </is>
       </c>
     </row>
@@ -518,22 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8731974074405733</v>
+        <v>0.8803448237643021</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02065888893166557</v>
+        <v>0.02388229304289909</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8647058823529411</v>
+        <v>0.8717647058823529</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01499711621644939</v>
+        <v>0.01784205986835659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8688356294898911</v>
+        <v>0.8759373401870401</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01476499533794843</v>
+        <v>0.01824121329192424</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9068870523415979</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01358688186849328</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9046831955922865</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01182489037539107</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.8975757575757577</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01032855811280698</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8949019607843139</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0213153579114026</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8717647058823529</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.01784205986835659</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8732941176470588</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01752484916715156</v>
       </c>
     </row>
     <row r="3">
@@ -571,22 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8747203944656079</v>
+        <v>0.8782798081385625</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0203224888085293</v>
+        <v>0.02010229097043379</v>
       </c>
       <c r="J3" t="n">
-        <v>0.868235294117647</v>
+        <v>0.8717647058823529</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008921029934178306</v>
+        <v>0.007669649888473726</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8713851733795137</v>
+        <v>0.8749290008202699</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01250164965122858</v>
+        <v>0.01182448467742477</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9024793388429753</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01311798176397693</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.008378460785534688</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8942699724517906</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.007846163358200733</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8927450980392158</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01876369165616064</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8717647058823529</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.007669649888473726</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8720784313725488</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01087625690412473</v>
       </c>
     </row>
     <row r="4">
@@ -624,22 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8791192945592762</v>
+        <v>0.8897740714784487</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01487780696917466</v>
+        <v>0.01425421643384677</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8705882352941176</v>
+        <v>0.8811764705882353</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007204381596421137</v>
+        <v>0.01052267283529308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8747423706983127</v>
+        <v>0.8853628040629241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006072130204107356</v>
+        <v>0.007469819193919331</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9168044077134987</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.008183719436646213</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9132231404958679</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.005843857695756603</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.9063911845730027</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.004875332629339787</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9058823529411766</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01071726034758594</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8811764705882353</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.01052267283529308</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8829411764705881</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.007270782830486026</v>
       </c>
     </row>
     <row r="5">
@@ -677,22 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8645742099555559</v>
+        <v>0.8775100394161154</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01207888556398817</v>
+        <v>0.01196811711289808</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8635294117647059</v>
+        <v>0.8764705882352942</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0134138285305781</v>
+        <v>0.01499711621644939</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8640294383150218</v>
+        <v>0.8769675496826699</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0117805250397328</v>
+        <v>0.01260740952843127</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.903305785123967</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01481596893611552</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.906060606060606</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01656905138699231</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.896198347107438</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01468270457471637</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8931372549019609</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01403707947380035</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8764705882352942</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.01499711621644939</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8750588235294116</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.01322505050214604</v>
       </c>
     </row>
     <row r="6">
@@ -730,22 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8930154480873498</v>
+        <v>0.9000083481139993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01530422007419065</v>
+        <v>0.0142295981959301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8754285714285714</v>
+        <v>0.8822857142857142</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007450517034517309</v>
+        <v>0.005111012519999476</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8840533646842171</v>
+        <v>0.8909770718826584</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007195390535008483</v>
+        <v>0.004445749697313689</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9185950413223141</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01081727718611412</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9112947658402204</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.002304848557945145</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9055175127902402</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.005689861863668954</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.9132380952380952</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01124555845807647</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8822857142857142</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.005111012519999476</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8862639455782311</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00190509229398958</v>
       </c>
     </row>
     <row r="7">
@@ -783,22 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8953930257315339</v>
+        <v>0.902445212154279</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005447757325491993</v>
+        <v>0.003900645984543614</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8708571428571428</v>
+        <v>0.8777142857142858</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0111391935369245</v>
+        <v>0.01038051549976284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8829442881317296</v>
+        <v>0.8898975172231118</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008204078337778456</v>
+        <v>0.007193178919388419</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.921625344352617</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.00694534558428577</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9090909090909089</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.008926640080451595</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9056985438803622</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.007500193014640676</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9181904761904762</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.00611121418177351</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8777142857142858</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01038051549976284</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.8855727891156461</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.007840569734342171</v>
       </c>
     </row>
     <row r="8">
@@ -836,22 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8935294867764922</v>
+        <v>0.8982219349511926</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005702521186294251</v>
+        <v>0.003890283886154553</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8731428571428571</v>
+        <v>0.8777142857142858</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01422845668341572</v>
+        <v>0.01251937274297526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8831973792864103</v>
+        <v>0.8878284365249127</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009876470609124612</v>
+        <v>0.008080746870227019</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9204132231404959</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0009412864773152325</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9107438016528926</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.007050404348247843</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9059858323494687</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.00471833407498946</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9132</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.003635676084247513</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8777142857142858</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.01251937274297526</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8833496598639456</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.009404295789952617</v>
       </c>
     </row>
     <row r="9">
@@ -889,22 +1201,58 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8815061522667778</v>
+        <v>0.8872742250121737</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01967145360129622</v>
+        <v>0.01680997623352175</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8651428571428571</v>
+        <v>0.8708571428571428</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01315527363796723</v>
+        <v>0.01376182237576262</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8731684704946007</v>
+        <v>0.8789092579082027</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01371372797948159</v>
+        <v>0.0120477230901258</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9111570247933883</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01265232305156602</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9041322314049587</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01150776780947954</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8969775678866589</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01149205764005685</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.9075238095238095</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.009327743710088137</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.8708571428571428</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01376182237576262</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.8762068027210883</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.010623221255317</v>
       </c>
     </row>
     <row r="10">
@@ -942,22 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8908909889044334</v>
+        <v>0.9001757156486743</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03289849238158567</v>
+        <v>0.02590507662507143</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8823529411764707</v>
+        <v>0.891764705882353</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02200974933396435</v>
+        <v>0.02338189048747271</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8861149667287579</v>
+        <v>0.8954621184107209</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01515117461747082</v>
+        <v>0.007840315657701097</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9242424242424244</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01650020461530428</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.9242424242424242</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0157350684005452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.9159228650137742</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.006274100903253436</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.9121568627450982</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01456798087922088</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.891764705882353</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02338189048747271</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.8920392156862744</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.009337534068674751</v>
       </c>
     </row>
     <row r="11">
@@ -995,22 +1379,58 @@
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8789496168983442</v>
+        <v>0.8894186761132783</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01649604979027871</v>
+        <v>0.01562401657238048</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8858823529411766</v>
+        <v>0.8964705882352941</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01533929977694741</v>
+        <v>0.01694689445986814</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8822575379890705</v>
+        <v>0.8927848348438969</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00969314459687466</v>
+        <v>0.01022947323102329</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9125344352617081</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.009860758308041522</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9179063360881543</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01005603980630511</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.9075324675324676</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.008085839769739403</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9075490196078432</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01067007226487424</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.8964705882352941</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01694689445986814</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8933389355742296</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01277222464871432</v>
       </c>
     </row>
     <row r="12">
@@ -1048,22 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8872473900721782</v>
+        <v>0.8967792577757188</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01440820615560866</v>
+        <v>0.01454114233803361</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8788235294117648</v>
+        <v>0.8882352941176471</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01146681687624583</v>
+        <v>0.008318903308077073</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8829948160036578</v>
+        <v>0.8924660113776348</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01210612575984625</v>
+        <v>0.0107792842936701</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.9247933884297522</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01312521129429372</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9223140495867769</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.006928251426974768</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.9164187327823692</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.009853251654197516</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9068627450980393</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.01367286831468767</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8882352941176471</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.008318903308077073</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8884313725490195</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.009091782838721269</v>
       </c>
     </row>
     <row r="13">
@@ -1101,22 +1557,58 @@
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8645179395512397</v>
+        <v>0.874991276535815</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02444732254586639</v>
+        <v>0.01693296279966751</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8694117647058824</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01684449536856042</v>
+        <v>0.00892102993417831</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8669377140319343</v>
+        <v>0.8774678204121094</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0205251873990517</v>
+        <v>0.0127262749644044</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.9027548209366392</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01163076134026702</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9085399449035814</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.005208724628426717</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8977961432506888</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.008808968019459714</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.8890196078431375</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01642559213220342</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.00892102993417831</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.8753725490196077</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01220231855997615</v>
       </c>
     </row>
     <row r="14">
@@ -1154,22 +1646,58 @@
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.883065996663974</v>
+        <v>0.8853916566714108</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01526158414311968</v>
+        <v>0.01515654054787948</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8720000000000001</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01833920746957855</v>
+        <v>0.01761261143705422</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8774910290685023</v>
+        <v>0.8797965237200206</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01666962174910225</v>
+        <v>0.01621419151896734</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.9046831955922865</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01576969567996872</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9046831955922865</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.01513272062476286</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8962770562770563</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.01562963260510396</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8940952380952382</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.01623453389238348</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01761261143705422</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8745251700680271</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.01779736830723916</v>
       </c>
     </row>
     <row r="15">
@@ -1207,22 +1735,58 @@
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8872390978094191</v>
+        <v>0.8907007390818062</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01032060156918886</v>
+        <v>0.01268675925030759</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8811428571428571</v>
+        <v>0.8845714285714286</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01099164803524074</v>
+        <v>0.01238827622210217</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8841704393986598</v>
+        <v>0.8876154407611363</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01012314080693502</v>
+        <v>0.01207706992131589</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9108815426997247</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01375342800701564</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.9118457300275482</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01035350990246072</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.9032821723730816</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01102169395128865</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.9012380952380953</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01680082062567611</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8845714285714286</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01238827622210217</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8839510204081632</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01293388034469835</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9001184456387323</v>
+        <v>0.9048492911497268</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02089861420112248</v>
+        <v>0.02164265160955101</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8708571428571428</v>
+        <v>0.8754285714285714</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008666143364630331</v>
+        <v>0.009389529557231454</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8850907750665644</v>
+        <v>0.8897395421112828</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008557867116036826</v>
+        <v>0.009615941428465049</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9246556473829202</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01595657350696926</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9112947658402204</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.008524379309512877</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.9092404565131839</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.01004812030471761</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.9136190476190477</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01777154085607361</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8754285714285714</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.009389529557231454</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8834721088435374</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.008219795197452619</v>
       </c>
     </row>
     <row r="17">
@@ -1313,22 +1913,58 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9072059066140454</v>
+        <v>0.910785814297261</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02044624060059865</v>
+        <v>0.02238769070902222</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8788571428571428</v>
+        <v>0.8822857142857142</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004780914437337544</v>
+        <v>0.003129843185743765</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8927096923291045</v>
+        <v>0.8962119617274906</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01003594171340425</v>
+        <v>0.01150214404769509</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9276859504132231</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01698185675749032</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.915977961432507</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.00567920885071305</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9141440377804015</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.01066816344139456</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.915904761904762</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.01945283265780845</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8822857142857142</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.003129843185743765</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8900244897959183</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.009763999396029097</v>
       </c>
     </row>
   </sheetData>
